--- a/tests/fixtures/compiler-mel.xlsx
+++ b/tests/fixtures/compiler-mel.xlsx
@@ -503,7 +503,7 @@
         <v>B14</v>
       </c>
       <c r="E4" s="2" t="str">
-        <v/>
+        <v>B14-AHU-7002</v>
       </c>
       <c r="F4" s="2" t="str">
         <v>Mechanical</v>

--- a/tests/fixtures/compiler-mel.xlsx
+++ b/tests/fixtures/compiler-mel.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -593,9 +593,35 @@
         <v>New</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>B14-FCU-7101</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>Fan coil unit</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>2201</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>B14</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>B14-AHU-7001</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>Mechanical</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>Screening</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <v>New</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/fixtures/compiler-mel.xlsx
+++ b/tests/fixtures/compiler-mel.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -619,9 +619,35 @@
         <v>New</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="str">
+        <v>B14-DDC-7301</v>
+      </c>
+      <c r="B9" s="2" t="str">
+        <v>DDC controller</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <v>650</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <v>B14</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F9" s="2" t="str">
+        <v>I&amp;C</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>FMS Network</v>
+      </c>
+      <c r="H9" s="2" t="str">
+        <v>New</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/fixtures/compiler-mel.xlsx
+++ b/tests/fixtures/compiler-mel.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -645,9 +645,61 @@
         <v>New</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="str">
+        <v>B14-TT-7001-02A</v>
+      </c>
+      <c r="B10" s="2" t="str">
+        <v>Temperature transmitter</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <v>2201</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <v>B14</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F10" s="2" t="str">
+        <v>Mechanical</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <v>Screening</v>
+      </c>
+      <c r="H10" s="2" t="str">
+        <v>New</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="str">
+        <v>B14-RIO-6500-PS1</v>
+      </c>
+      <c r="B11" s="2" t="str">
+        <v>RIO power supply</v>
+      </c>
+      <c r="C11" s="2" t="str">
+        <v>650</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <v>B14</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F11" s="2" t="str">
+        <v>I&amp;C</v>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>FMS Network</v>
+      </c>
+      <c r="H11" s="2" t="str">
+        <v>New</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/fixtures/compiler-mel.xlsx
+++ b/tests/fixtures/compiler-mel.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -697,9 +697,35 @@
         <v>New</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="str">
+        <v>B14-PT-7001-01</v>
+      </c>
+      <c r="B12" s="2" t="str">
+        <v>Pressure transmitter</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <v>2201</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <v>B14</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F12" s="2" t="str">
+        <v>Mechanical</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <v>Screening</v>
+      </c>
+      <c r="H12" s="2" t="str">
+        <v>New</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/fixtures/compiler-mel.xlsx
+++ b/tests/fixtures/compiler-mel.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -723,9 +723,35 @@
         <v>New</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="str">
+        <v>B14-PT-7001-02</v>
+      </c>
+      <c r="B13" s="2" t="str">
+        <v>Pressure transmitter</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <v>2201</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <v>B14</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F13" s="2" t="str">
+        <v>Mechanical</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <v>Screening</v>
+      </c>
+      <c r="H13" s="2" t="str">
+        <v>New</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>